--- a/zara周报数据源/热词部分/0421-0427热词/家居.xlsx
+++ b/zara周报数据源/热词部分/0421-0427热词/家居.xlsx
@@ -125,8 +125,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A3:N6">
-  <autoFilter ref="A3:N6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A3:N12">
+  <autoFilter ref="A3:N12"/>
   <tableColumns count="14">
     <tableColumn id="1" name="家居热词分类"/>
     <tableColumn id="2" name="上架天数"/>
@@ -450,11 +450,9 @@
     <row r="1">
       <c t="str">
         <v>应用的筛选器: 
-搜索PV 大于 20
-hotword_audiocontent.1 不等于 毛巾、连体衣、连衣裙、显瘦牛仔裤、挂钩、衬衫合集 或 
 category 等于 家居
+Date 在 2026/4/21 当天或之后 和 在 2026/4/28 之前
 Search Entrance 等于 热词搜索
-Date 在 2026/4/21 当天或之后 和 在 2026/4/28 之前
 handlemodule 不等于 推荐产品
 Search Entrance 等于 热词搜索
 audiocontent2 不为空
@@ -615,6 +613,270 @@
       </c>
       <c s="12">
         <v>0.32</v>
+      </c>
+      <c s="13">
+        <v/>
+      </c>
+      <c s="14">
+        <v/>
+      </c>
+      <c s="15">
+        <v/>
+      </c>
+      <c s="16">
+        <v/>
+      </c>
+      <c s="17">
+        <v/>
+      </c>
+      <c s="18">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c t="str">
+        <v>玻璃杯</v>
+      </c>
+      <c s="6">
+        <v>7</v>
+      </c>
+      <c s="7">
+        <v>17</v>
+      </c>
+      <c s="8">
+        <v>12</v>
+      </c>
+      <c s="9">
+        <v>1.41666666666667</v>
+      </c>
+      <c s="10">
+        <v>5</v>
+      </c>
+      <c s="11">
+        <v>3</v>
+      </c>
+      <c s="12">
+        <v>0.25</v>
+      </c>
+      <c s="13">
+        <v>3</v>
+      </c>
+      <c s="14">
+        <v>2</v>
+      </c>
+      <c s="15">
+        <v>0.166666666666667</v>
+      </c>
+      <c s="16">
+        <v>1</v>
+      </c>
+      <c s="17">
+        <v>1</v>
+      </c>
+      <c s="18">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="8">
+      <c t="str">
+        <v>收纳篮</v>
+      </c>
+      <c s="6">
+        <v>6</v>
+      </c>
+      <c s="7">
+        <v>14</v>
+      </c>
+      <c s="8">
+        <v>9</v>
+      </c>
+      <c s="9">
+        <v>1.55555555555556</v>
+      </c>
+      <c s="10">
+        <v>3</v>
+      </c>
+      <c s="11">
+        <v>1</v>
+      </c>
+      <c s="12">
+        <v>0.111111111111111</v>
+      </c>
+      <c s="13">
+        <v/>
+      </c>
+      <c s="14">
+        <v/>
+      </c>
+      <c s="15">
+        <v/>
+      </c>
+      <c s="16">
+        <v/>
+      </c>
+      <c s="17">
+        <v/>
+      </c>
+      <c s="18">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c t="str">
+        <v>毛绒玩具</v>
+      </c>
+      <c s="6">
+        <v>6</v>
+      </c>
+      <c s="7">
+        <v>12</v>
+      </c>
+      <c s="8">
+        <v>11</v>
+      </c>
+      <c s="9">
+        <v>1.09090909090909</v>
+      </c>
+      <c s="10">
+        <v>3</v>
+      </c>
+      <c s="11">
+        <v>3</v>
+      </c>
+      <c s="12">
+        <v>0.272727272727273</v>
+      </c>
+      <c s="13">
+        <v>1</v>
+      </c>
+      <c s="14">
+        <v>1</v>
+      </c>
+      <c s="15">
+        <v>0.0909090909090909</v>
+      </c>
+      <c s="16">
+        <v/>
+      </c>
+      <c s="17">
+        <v/>
+      </c>
+      <c s="18">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c t="str">
+        <v>马克杯</v>
+      </c>
+      <c s="6">
+        <v>6</v>
+      </c>
+      <c s="7">
+        <v>9</v>
+      </c>
+      <c s="8">
+        <v>9</v>
+      </c>
+      <c s="9">
+        <v>1</v>
+      </c>
+      <c s="10">
+        <v>1</v>
+      </c>
+      <c s="11">
+        <v>1</v>
+      </c>
+      <c s="12">
+        <v>0.111111111111111</v>
+      </c>
+      <c s="13">
+        <v/>
+      </c>
+      <c s="14">
+        <v/>
+      </c>
+      <c s="15">
+        <v/>
+      </c>
+      <c s="16">
+        <v/>
+      </c>
+      <c s="17">
+        <v/>
+      </c>
+      <c s="18">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c t="str">
+        <v>迷你小盘</v>
+      </c>
+      <c s="6">
+        <v>4</v>
+      </c>
+      <c s="7">
+        <v>9</v>
+      </c>
+      <c s="8">
+        <v>8</v>
+      </c>
+      <c s="9">
+        <v>1.125</v>
+      </c>
+      <c s="10">
+        <v>1</v>
+      </c>
+      <c s="11">
+        <v>1</v>
+      </c>
+      <c s="12">
+        <v>0.125</v>
+      </c>
+      <c s="13">
+        <v/>
+      </c>
+      <c s="14">
+        <v/>
+      </c>
+      <c s="15">
+        <v/>
+      </c>
+      <c s="16">
+        <v/>
+      </c>
+      <c s="17">
+        <v/>
+      </c>
+      <c s="18">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c t="str">
+        <v>%E5%B0%8F%E7%8B%97%E7%B3%BB%E5%88%97</v>
+      </c>
+      <c s="6">
+        <v>1</v>
+      </c>
+      <c s="7">
+        <v>1</v>
+      </c>
+      <c s="8">
+        <v>1</v>
+      </c>
+      <c s="9">
+        <v>1</v>
+      </c>
+      <c s="10">
+        <v/>
+      </c>
+      <c s="11">
+        <v/>
+      </c>
+      <c s="12">
+        <v/>
       </c>
       <c s="13">
         <v/>
